--- a/public/outils/matrices/net-vendeur-honoraires-et-qualification.xlsx
+++ b/public/outils/matrices/net-vendeur-honoraires-et-qualification.xlsx
@@ -34,7 +34,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="562">
   <si>
-    <t>CorpusImmo  ·  corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
+    <t>CorpusImmo  ·  www.corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
   </si>
   <si>
     <t>Mode d'emploi</t>
@@ -118,7 +118,7 @@
     <t>Net vendeur</t>
   </si>
   <si>
-    <t>Vous remplissez les quatre blocs bleus, de haut en bas : la vente, le prêt et les frais, le bien et son acquisition, les exonérations.</t>
+    <t>Vous remplissez les quatre blocs violets, de haut en bas : la vente, le prêt et les frais, le bien et son acquisition, les exonérations.</t>
   </si>
   <si>
     <t>Quatre contrôles de bloc (Net vendeur!C12, Net vendeur!C21, Net vendeur!C34, Net vendeur!C42) et le contrôle général (Net vendeur!C65), puis la plus-value, l'impôt et le net en poche (Net vendeur!C62).</t>
@@ -163,7 +163,7 @@
     <t>Ce que vous faites</t>
   </si>
   <si>
-    <t>Fond bleu ciel</t>
+    <t>Fond violet clair</t>
   </si>
   <si>
     <t>Saisie utilisateur</t>
@@ -181,7 +181,7 @@
     <t>Vous la lisez. Elle est verrouillée.</t>
   </si>
   <si>
-    <t>Fond bleu très pâle, gras</t>
+    <t>Fond violet très pâle, gras</t>
   </si>
   <si>
     <t>Résultat de bloc ou chiffre clé</t>
@@ -235,7 +235,7 @@
     <t>Net vendeur et Qualifier le mandat</t>
   </si>
   <si>
-    <t>Le classeur est livré rempli d'un cas complet. Gardez-le le temps de vous repérer, puis effacez les cellules bleues de chiffres et de dates de l'onglet Net vendeur, ainsi que les notes de Qualifier le mandat!C8:C15 et l'écart de prix de Qualifier le mandat!C18, avant de saisir votre dossier. Ne touchez ni aux poids de Qualifier le mandat!D8:D15, qui sont votre grille et pas votre dossier, ni aux cellules bleues de l'onglet Paramètres, qui sont vos barèmes. N'effacez jamais les cellules d'option, celles qui se choisissent dans une liste : une option vide fait passer le contrôle au rouge et vide tout le calcul. Remplacez-les, ne les videz pas.</t>
+    <t>Le classeur est livré rempli d'un cas complet. Gardez-le le temps de vous repérer, puis effacez les cellules violettes de chiffres et de dates de l'onglet Net vendeur, ainsi que les notes de Qualifier le mandat!C8:C15 et l'écart de prix de Qualifier le mandat!C18, avant de saisir votre dossier. Ne touchez ni aux poids de Qualifier le mandat!D8:D15, qui sont votre grille et pas votre dossier, ni aux cellules violettes de l'onglet Paramètres, qui sont vos barèmes. N'effacez jamais les cellules d'option, celles qui se choisissent dans une liste : une option vide fait passer le contrôle au rouge et vide tout le calcul. Remplacez-les, ne les videz pas.</t>
   </si>
   <si>
     <t>Une saisie oubliée de l'exemple est l'erreur la plus probable d'un premier usage. Regardez surtout les travaux, les frais réels et l'indemnité de remboursement anticipé, qui n'ont aucune raison d'exister dans votre dossier. Les plages indiquées ci-dessous sautent les cellules calculées : suivez-les telles quelles plutôt que de sélectionner une colonne entière, la feuille est protégée et refusera d'effacer une formule.</t>
@@ -622,7 +622,7 @@
     <t>À changer le jour où vous relisez les barèmes. Fréquence : à chaque relecture des barèmes.</t>
   </si>
   <si>
-    <t>L'architecture ne change jamais quand les données changent : seules les cellules bleues de Paramètres bougent, les formules pointent dessus. Les chiffres cités dans ce guide et dans l'onglet Méthode sont du millésime 2026 : relisez-les à chaque mise à jour de Paramètres, en particulier l'exemple guidé et le tableau des repères ci-dessus.</t>
+    <t>L'architecture ne change jamais quand les données changent : seules les cellules violettes de Paramètres bougent, les formules pointent dessus. Les chiffres cités dans ce guide et dans l'onglet Méthode sont du millésime 2026 : relisez-les à chaque mise à jour de Paramètres, en particulier l'exemple guidé et le tableau des repères ci-dessus.</t>
   </si>
   <si>
     <t xml:space="preserve">  TROIS FAÇONS DE S'EN SERVIR</t>
@@ -712,7 +712,7 @@
     <t>Du prix affiché au virement du notaire : honoraires, solde de prêt, impôt de plus-value et net en poche.</t>
   </si>
   <si>
-    <t>Cellules bleues : à remplir.  Cellules blanches : calculées automatiquement.</t>
+    <t>Cellules violettes : à remplir.  Cellules blanches : calculées automatiquement.</t>
   </si>
   <si>
     <t xml:space="preserve">  LA VENTE</t>
@@ -1543,7 +1543,7 @@
     <t>Aucun de ces taux n'est recopié dans une formule : toutes pointent ici.</t>
   </si>
   <si>
-    <t>Les libellés des listes ci-dessus sont fixes : les formules comparent leur texte. Les modifier casse le classeur ; les valeurs bleues, elles, se mettent à jour librement.</t>
+    <t>Les libellés des listes ci-dessus sont fixes : les formules comparent leur texte. Les modifier casse le classeur ; les valeurs violettes, elles, se mettent à jour librement.</t>
   </si>
   <si>
     <t>Vérifiez les barèmes chaque janvier, après la loi de finances et la loi de financement de la sécurité sociale, puis mettez à jour la date ci-dessus : toutes les mentions « Vérifié le » et « Consulté le » de cet onglet la lisent.</t>
@@ -1748,7 +1748,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1768,19 +1768,19 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1798,7 +1798,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1811,17 +1811,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E1A33"/>
+        <fgColor rgb="FF4B3D7C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
+        <fgColor rgb="FFF1EEF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F9FF"/>
+        <fgColor rgb="FFF8F6FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -2211,6 +2211,171 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10163175" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10163175" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8658225" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8658225" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="16354425" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16354425" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8782050" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8782050" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3589,6 +3754,7 @@
     <mergeCell ref="C12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4284,6 +4450,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
@@ -4728,6 +4895,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6072,6 +6240,7 @@
     <mergeCell ref="B110:F110"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6465,5 +6634,6 @@
     <mergeCell ref="B27:C27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>